--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_17-03-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_17-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="351">
   <si>
     <t>SKU</t>
   </si>
@@ -394,16 +394,16 @@
     <t>£431.80</t>
   </si>
   <si>
-    <t>£695.10</t>
-  </si>
-  <si>
-    <t>£158.15</t>
-  </si>
-  <si>
-    <t>£148.40</t>
-  </si>
-  <si>
-    <t>£134.60</t>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/rockwool-rw5-1200mm-x-600mm-all-sizes?variant=31690144972853</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/kingspan-thermafloor-tf70-floor-board-all-sizes?variant=31690185539637</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/kingspan-thermafloor-tf70-floor-board-all-sizes?variant=31690185637941</t>
+  </si>
+  <si>
+    <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/kingspan-thermafloor-tf70-floor-board-all-sizes?variant=31690185736245</t>
   </si>
   <si>
     <t>£112.20</t>
@@ -529,8 +529,88 @@
     <t>£12.00</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: 
-</t>
+    <t>£29.99 presale price: £34.99</t>
+  </si>
+  <si>
+    <t>£43.33</t>
+  </si>
+  <si>
+    <t>£43.99</t>
+  </si>
+  <si>
+    <t>£62.49</t>
+  </si>
+  <si>
+    <t>£59.99</t>
+  </si>
+  <si>
+    <t>£39.16 presale price: £41.66</t>
+  </si>
+  <si>
+    <t>£63.91</t>
+  </si>
+  <si>
+    <t>£22.49</t>
+  </si>
+  <si>
+    <t>£33.33 presale price: £41.66</t>
+  </si>
+  <si>
+    <t>£1290.75</t>
+  </si>
+  <si>
+    <t>£29.73</t>
+  </si>
+  <si>
+    <t>£28.38</t>
+  </si>
+  <si>
+    <t>£22.53</t>
+  </si>
+  <si>
+    <t>£45.12</t>
+  </si>
+  <si>
+    <t>£43.72</t>
+  </si>
+  <si>
+    <t>£41.37</t>
+  </si>
+  <si>
+    <t>£35.67</t>
+  </si>
+  <si>
+    <t>£812.4</t>
+  </si>
+  <si>
+    <t>£830.4</t>
+  </si>
+  <si>
+    <t>£648.96</t>
+  </si>
+  <si>
+    <t>£399.96 presale price: £540.7</t>
+  </si>
+  <si>
+    <t>£976.56</t>
+  </si>
+  <si>
+    <t>£155.72</t>
+  </si>
+  <si>
+    <t>£114.6</t>
+  </si>
+  <si>
+    <t>£80.88</t>
+  </si>
+  <si>
+    <t>£9.23</t>
+  </si>
+  <si>
+    <t>£11.25</t>
+  </si>
+  <si>
+    <t>£9.58</t>
   </si>
   <si>
     <t>£27.88</t>
@@ -827,16 +907,16 @@
     <t>£29.5</t>
   </si>
   <si>
-    <t>£45.29</t>
-  </si>
-  <si>
-    <t>£46.66</t>
+    <t>£41.22</t>
+  </si>
+  <si>
+    <t>£39.16</t>
   </si>
   <si>
     <t>£60.03</t>
   </si>
   <si>
-    <t>£53.77</t>
+    <t>£49.97</t>
   </si>
   <si>
     <t>£36.06</t>
@@ -863,7 +943,7 @@
     <t>£38.0</t>
   </si>
   <si>
-    <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+    <t>£591.96</t>
   </si>
   <si>
     <t>£554.76</t>
@@ -969,9 +1049,6 @@
   </si>
   <si>
     <t>£9.12</t>
-  </si>
-  <si>
-    <t>Error: 'NoneType' object has no attribute 'find'</t>
   </si>
   <si>
     <t>£13.11</t>
@@ -1399,19 +1476,19 @@
         <v>171</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="G2" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="H2" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="I2" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J2" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1431,19 +1508,19 @@
         <v>171</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="G3" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="H3" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="I3" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J3" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1460,19 +1537,19 @@
         <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="G4" t="s">
         <v>153</v>
       </c>
       <c r="H4" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="I4" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="J4" t="s">
         <v>153</v>
@@ -1495,19 +1572,19 @@
         <v>171</v>
       </c>
       <c r="F5" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="H5" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="I5" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J5" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1524,22 +1601,22 @@
         <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F6" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="G6" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="H6" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="I6" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="J6" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1556,22 +1633,22 @@
         <v>148</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="G7" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="H7" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="I7" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="J7" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1588,22 +1665,22 @@
         <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="G8" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="H8" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="I8" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="J8" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1620,22 +1697,22 @@
         <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="G9" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="H9" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="I9" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="J9" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1652,22 +1729,22 @@
         <v>151</v>
       </c>
       <c r="E10" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="G10" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="H10" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="I10" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="J10" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1684,22 +1761,22 @@
         <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="G11" t="s">
         <v>153</v>
       </c>
       <c r="H11" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="I11" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1716,19 +1793,19 @@
         <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F12" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="H12" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="I12" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="J12" t="s">
         <v>153</v>
@@ -1748,22 +1825,22 @@
         <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F13" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="G13" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="H13" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="I13" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="J13" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1780,22 +1857,22 @@
         <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F14" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="G14" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="H14" t="s">
         <v>112</v>
       </c>
       <c r="I14" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="J14" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1812,22 +1889,22 @@
         <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="G15" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="H15" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="I15" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="J15" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1844,22 +1921,22 @@
         <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="H16" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="I16" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="J16" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1876,22 +1953,22 @@
         <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="G17" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H17" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="I17" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="J17" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1908,22 +1985,22 @@
         <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F18" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="G18" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="H18" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="I18" t="s">
         <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1940,22 +2017,22 @@
         <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F19" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="G19" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="H19" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="I19" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="J19" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1972,22 +2049,22 @@
         <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G20" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="H20" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="I20" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="J20" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -2004,22 +2081,22 @@
         <v>158</v>
       </c>
       <c r="E21" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="G21" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="H21" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="I21" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="J21" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2036,16 +2113,16 @@
         <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="F22" t="s">
         <v>153</v>
       </c>
       <c r="G22" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H22" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="I22" t="s">
         <v>153</v>
@@ -2068,16 +2145,16 @@
         <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F23" t="s">
         <v>153</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H23" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="I23" t="s">
         <v>153</v>
@@ -2100,16 +2177,16 @@
         <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="F24" t="s">
         <v>153</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="H24" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="I24" t="s">
         <v>153</v>
@@ -2132,22 +2209,22 @@
         <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="F25" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="G25" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="H25" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="I25" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="J25" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2164,22 +2241,22 @@
         <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="G26" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="H26" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="I26" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="J26" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2196,22 +2273,22 @@
         <v>161</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="G27" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="H27" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="I27" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="J27" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2228,22 +2305,22 @@
         <v>153</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="F28" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="G28" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="H28" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="I28" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="J28" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2263,19 +2340,19 @@
         <v>153</v>
       </c>
       <c r="F29" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="G29" t="s">
         <v>153</v>
       </c>
       <c r="H29" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="I29" t="s">
         <v>152</v>
       </c>
       <c r="J29" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2295,19 +2372,19 @@
         <v>153</v>
       </c>
       <c r="F30" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="G30" t="s">
         <v>153</v>
       </c>
       <c r="H30" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="I30" t="s">
         <v>152</v>
       </c>
       <c r="J30" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2327,19 +2404,19 @@
         <v>153</v>
       </c>
       <c r="F31" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="G31" t="s">
         <v>153</v>
       </c>
       <c r="H31" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="I31" t="s">
         <v>152</v>
       </c>
       <c r="J31" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2359,19 +2436,19 @@
         <v>153</v>
       </c>
       <c r="F32" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="G32" t="s">
         <v>153</v>
       </c>
       <c r="H32" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="I32" t="s">
         <v>152</v>
       </c>
       <c r="J32" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2388,22 +2465,22 @@
         <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F33" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="G33" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="H33" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="I33" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="J33" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2420,22 +2497,22 @@
         <v>166</v>
       </c>
       <c r="E34" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F34" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="G34" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="H34" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="I34" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="J34" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2452,22 +2529,22 @@
         <v>167</v>
       </c>
       <c r="E35" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="F35" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="G35" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="H35" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="I35" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="J35" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2484,22 +2561,22 @@
         <v>168</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="F36" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="G36" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="H36" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="I36" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="J36" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2516,22 +2593,22 @@
         <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="G37" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="H37" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="I37" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="J37" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2548,22 +2625,22 @@
         <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="G38" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="H38" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="I38" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="J38" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2580,22 +2657,22 @@
         <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="F39" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="H39" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="I39" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="J39" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2627,7 +2704,7 @@
         <v>153</v>
       </c>
       <c r="J40" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2659,7 +2736,7 @@
         <v>153</v>
       </c>
       <c r="J41" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2723,7 +2800,7 @@
         <v>153</v>
       </c>
       <c r="J43" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2755,7 +2832,7 @@
         <v>153</v>
       </c>
       <c r="J44" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2787,7 +2864,7 @@
         <v>153</v>
       </c>
       <c r="J45" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2819,7 +2896,7 @@
         <v>153</v>
       </c>
       <c r="J46" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
